--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/43.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/43.xlsx
@@ -426,13 +426,13 @@
         <v>-5.91791334041876</v>
       </c>
       <c r="E2">
-        <v>-15.58890704171819</v>
+        <v>-31.38826604352424</v>
       </c>
       <c r="F2">
-        <v>-3.412974079237209</v>
+        <v>-6.282360481815132</v>
       </c>
       <c r="G2">
-        <v>-12.64750020651217</v>
+        <v>-18.91400503112294</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.321989990768408</v>
       </c>
       <c r="E3">
-        <v>-16.28695319610454</v>
+        <v>-30.49243878685288</v>
       </c>
       <c r="F3">
-        <v>-3.267824229449069</v>
+        <v>-6.476254783053607</v>
       </c>
       <c r="G3">
-        <v>-12.30855658186465</v>
+        <v>-18.24957079022162</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.750470022544729</v>
       </c>
       <c r="E4">
-        <v>-16.14042083416435</v>
+        <v>-32.26157093471845</v>
       </c>
       <c r="F4">
-        <v>-3.32054153096323</v>
+        <v>-6.120425837527767</v>
       </c>
       <c r="G4">
-        <v>-12.04511058407839</v>
+        <v>-18.66140511120143</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.135403362891448</v>
       </c>
       <c r="E5">
-        <v>-16.57484640266818</v>
+        <v>-34.23122844011767</v>
       </c>
       <c r="F5">
-        <v>-3.137059807977945</v>
+        <v>-5.902922236942103</v>
       </c>
       <c r="G5">
-        <v>-12.3779544178469</v>
+        <v>-19.44448832369227</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.479734157199899</v>
       </c>
       <c r="E6">
-        <v>-17.24529603645179</v>
+        <v>-32.28645942786461</v>
       </c>
       <c r="F6">
-        <v>-3.066640295065959</v>
+        <v>-6.025373163158732</v>
       </c>
       <c r="G6">
-        <v>-11.80852466597775</v>
+        <v>-19.62855993134477</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.765443603188732</v>
       </c>
       <c r="E7">
-        <v>-17.42474134747973</v>
+        <v>-32.54785200453535</v>
       </c>
       <c r="F7">
-        <v>-3.182077434483084</v>
+        <v>-5.426942327293507</v>
       </c>
       <c r="G7">
-        <v>-12.08619804044576</v>
+        <v>-19.74662812671827</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.991685216478317</v>
       </c>
       <c r="E8">
-        <v>-18.21362416198595</v>
+        <v>-33.74314951157096</v>
       </c>
       <c r="F8">
-        <v>-2.875776161786924</v>
+        <v>-6.316073792557968</v>
       </c>
       <c r="G8">
-        <v>-12.2114389861482</v>
+        <v>-19.77185907989962</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.147857681381987</v>
       </c>
       <c r="E9">
-        <v>-18.51006712747607</v>
+        <v>-36.27930326567071</v>
       </c>
       <c r="F9">
-        <v>-3.083143030464531</v>
+        <v>-6.296775317174948</v>
       </c>
       <c r="G9">
-        <v>-11.84744979733744</v>
+        <v>-20.17156108416338</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.233837667550874</v>
       </c>
       <c r="E10">
-        <v>-19.43414753348128</v>
+        <v>-33.0083208270573</v>
       </c>
       <c r="F10">
-        <v>-2.893242288474952</v>
+        <v>-6.467387938374041</v>
       </c>
       <c r="G10">
-        <v>-11.09687364683602</v>
+        <v>-19.83919466813177</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.244101886314597</v>
       </c>
       <c r="E11">
-        <v>-19.7958322239999</v>
+        <v>-34.94240037641525</v>
       </c>
       <c r="F11">
-        <v>-2.945256306064136</v>
+        <v>-6.057237143674818</v>
       </c>
       <c r="G11">
-        <v>-10.95313317398143</v>
+        <v>-19.7769909104186</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.183651541519612</v>
       </c>
       <c r="E12">
-        <v>-20.41283680754499</v>
+        <v>-35.80861367731345</v>
       </c>
       <c r="F12">
-        <v>-2.836044347679049</v>
+        <v>-5.691316612264373</v>
       </c>
       <c r="G12">
-        <v>-10.5462682630534</v>
+        <v>-18.95485459892725</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.055922027337497</v>
       </c>
       <c r="E13">
-        <v>-21.07753075086485</v>
+        <v>-33.5610437220635</v>
       </c>
       <c r="F13">
-        <v>-2.759029373505974</v>
+        <v>-5.660157572408069</v>
       </c>
       <c r="G13">
-        <v>-10.33617164660216</v>
+        <v>-18.30208838189132</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.875842755228462</v>
       </c>
       <c r="E14">
-        <v>-21.70279074252592</v>
+        <v>-37.36995453110006</v>
       </c>
       <c r="F14">
-        <v>-2.572073477633348</v>
+        <v>-5.101389796156288</v>
       </c>
       <c r="G14">
-        <v>-9.387065185646534</v>
+        <v>-18.5129905382354</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.656745662497386</v>
       </c>
       <c r="E15">
-        <v>-22.42120597299878</v>
+        <v>-36.57256044969643</v>
       </c>
       <c r="F15">
-        <v>-2.589484103705388</v>
+        <v>-5.553118421720526</v>
       </c>
       <c r="G15">
-        <v>-9.205062388187255</v>
+        <v>-17.72636032523881</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.419465403108929</v>
       </c>
       <c r="E16">
-        <v>-23.0199336354489</v>
+        <v>-36.94970082200323</v>
       </c>
       <c r="F16">
-        <v>-1.975875920286071</v>
+        <v>-5.52305365520332</v>
       </c>
       <c r="G16">
-        <v>-8.673199341952182</v>
+        <v>-16.25007148060266</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.178753268736171</v>
       </c>
       <c r="E17">
-        <v>-24.64512144426966</v>
+        <v>-37.27847935614512</v>
       </c>
       <c r="F17">
-        <v>-1.805218153063525</v>
+        <v>-5.579651857999597</v>
       </c>
       <c r="G17">
-        <v>-8.203065916914943</v>
+        <v>-17.89853750473833</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.949775745482111</v>
       </c>
       <c r="E18">
-        <v>-24.67304401500095</v>
+        <v>-38.44857590532803</v>
       </c>
       <c r="F18">
-        <v>-2.094781434018717</v>
+        <v>-4.682811605684684</v>
       </c>
       <c r="G18">
-        <v>-8.176642239696735</v>
+        <v>-15.82803748240532</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.73739793002618</v>
       </c>
       <c r="E19">
-        <v>-25.63952905161399</v>
+        <v>-38.30445722003392</v>
       </c>
       <c r="F19">
-        <v>-1.283880157907239</v>
+        <v>-4.565861039022644</v>
       </c>
       <c r="G19">
-        <v>-7.773419484699692</v>
+        <v>-14.12003369307353</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.545123027338064</v>
       </c>
       <c r="E20">
-        <v>-25.94101673714865</v>
+        <v>-37.29968393568603</v>
       </c>
       <c r="F20">
-        <v>-1.419781285643123</v>
+        <v>-5.085857078986394</v>
       </c>
       <c r="G20">
-        <v>-8.242132140801692</v>
+        <v>-16.72818483647247</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.370606286111276</v>
       </c>
       <c r="E21">
-        <v>-26.67327551266296</v>
+        <v>-37.6917954430622</v>
       </c>
       <c r="F21">
-        <v>-0.9326018487086779</v>
+        <v>-4.73877942088743</v>
       </c>
       <c r="G21">
-        <v>-7.745893317037511</v>
+        <v>-15.64373290802209</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.21296556133523</v>
       </c>
       <c r="E22">
-        <v>-27.30037859324515</v>
+        <v>-38.03653458384412</v>
       </c>
       <c r="F22">
-        <v>-1.049168052895819</v>
+        <v>-5.11967103636867</v>
       </c>
       <c r="G22">
-        <v>-6.992216412162416</v>
+        <v>-16.67779183576252</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.071358159548089</v>
       </c>
       <c r="E23">
-        <v>-28.05768435849588</v>
+        <v>-38.75168025608343</v>
       </c>
       <c r="F23">
-        <v>-0.660819474054577</v>
+        <v>-5.168683878857512</v>
       </c>
       <c r="G23">
-        <v>-6.80783144785098</v>
+        <v>-16.4013325132715</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.947165267247922</v>
       </c>
       <c r="E24">
-        <v>-27.29310133551482</v>
+        <v>-39.14145733510864</v>
       </c>
       <c r="F24">
-        <v>-0.7342625279867812</v>
+        <v>-4.364369780333095</v>
       </c>
       <c r="G24">
-        <v>-7.132078481133747</v>
+        <v>-16.02877277374747</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.847250464733159</v>
       </c>
       <c r="E25">
-        <v>-27.18399228277401</v>
+        <v>-38.27267638944809</v>
       </c>
       <c r="F25">
-        <v>-0.5812324190958089</v>
+        <v>-4.81961565388962</v>
       </c>
       <c r="G25">
-        <v>-6.710431667080423</v>
+        <v>-15.30496154750644</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.778011618479181</v>
       </c>
       <c r="E26">
-        <v>-27.72730953726629</v>
+        <v>-38.09686970728531</v>
       </c>
       <c r="F26">
-        <v>0.0240374180469283</v>
+        <v>-4.689696995536753</v>
       </c>
       <c r="G26">
-        <v>-7.058506931327878</v>
+        <v>-15.54472860990897</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.74818663978023</v>
       </c>
       <c r="E27">
-        <v>-28.38903280163712</v>
+        <v>-38.62887709794343</v>
       </c>
       <c r="F27">
-        <v>-0.3760640375052329</v>
+        <v>-3.752961740735614</v>
       </c>
       <c r="G27">
-        <v>-7.167955357664716</v>
+        <v>-16.28059176293783</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.757148338173474</v>
       </c>
       <c r="E28">
-        <v>-28.50973927631157</v>
+        <v>-36.85803318690296</v>
       </c>
       <c r="F28">
-        <v>-0.4218296797751</v>
+        <v>-3.470106579008291</v>
       </c>
       <c r="G28">
-        <v>-8.075610146659873</v>
+        <v>-16.67952103952435</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.803458698424395</v>
       </c>
       <c r="E29">
-        <v>-27.71678083519845</v>
+        <v>-38.85298448387203</v>
       </c>
       <c r="F29">
-        <v>-0.4783384188918739</v>
+        <v>-4.861439924056967</v>
       </c>
       <c r="G29">
-        <v>-7.755572920637873</v>
+        <v>-17.50385412884974</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.876619252574084</v>
       </c>
       <c r="E30">
-        <v>-27.02874713684306</v>
+        <v>-38.91056629511656</v>
       </c>
       <c r="F30">
-        <v>-0.4415605629423814</v>
+        <v>-4.683634174515664</v>
       </c>
       <c r="G30">
-        <v>-8.024954648225165</v>
+        <v>-16.46801021658098</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.96656002784411</v>
       </c>
       <c r="E31">
-        <v>-27.59876880255856</v>
+        <v>-38.37380853522439</v>
       </c>
       <c r="F31">
-        <v>-0.4387176060159735</v>
+        <v>-3.828110403150182</v>
       </c>
       <c r="G31">
-        <v>-8.2185631263402</v>
+        <v>-14.38936620233743</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.057544782816243</v>
       </c>
       <c r="E32">
-        <v>-26.51020063517274</v>
+        <v>-38.34001253370515</v>
       </c>
       <c r="F32">
-        <v>-0.2070621767208834</v>
+        <v>-4.420662315557738</v>
       </c>
       <c r="G32">
-        <v>-8.080279324938962</v>
+        <v>-15.58645098264809</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.136972865891391</v>
       </c>
       <c r="E33">
-        <v>-26.48013156776181</v>
+        <v>-38.79554531955873</v>
       </c>
       <c r="F33">
-        <v>-0.208724710098302</v>
+        <v>-4.622764909390553</v>
       </c>
       <c r="G33">
-        <v>-7.976031634773844</v>
+        <v>-15.94816136308581</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.189271360777584</v>
       </c>
       <c r="E34">
-        <v>-26.0322020897671</v>
+        <v>-36.55818480895908</v>
       </c>
       <c r="F34">
-        <v>-0.2010681101942262</v>
+        <v>-3.321847037990042</v>
       </c>
       <c r="G34">
-        <v>-7.739452279116321</v>
+        <v>-15.30491889162617</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.203164849345472</v>
       </c>
       <c r="E35">
-        <v>-25.9101687722084</v>
+        <v>-37.08723510609019</v>
       </c>
       <c r="F35">
-        <v>-0.2637283056441891</v>
+        <v>-4.657407234175628</v>
       </c>
       <c r="G35">
-        <v>-8.125688150100117</v>
+        <v>-15.79217373076059</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.166767008247968</v>
       </c>
       <c r="E36">
-        <v>-25.40176605231527</v>
+        <v>-39.42983055991709</v>
       </c>
       <c r="F36">
-        <v>-0.5242722197445092</v>
+        <v>-5.28363393824179</v>
       </c>
       <c r="G36">
-        <v>-7.611199172022305</v>
+        <v>-15.44050552890555</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.075139036775469</v>
       </c>
       <c r="E37">
-        <v>-25.71673500497077</v>
+        <v>-37.08902385332322</v>
       </c>
       <c r="F37">
-        <v>-0.3942947473060444</v>
+        <v>-4.169922958036953</v>
       </c>
       <c r="G37">
-        <v>-7.687901007195885</v>
+        <v>-17.24558097685195</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.924500194177491</v>
       </c>
       <c r="E38">
-        <v>-24.24832749476957</v>
+        <v>-35.27524321597902</v>
       </c>
       <c r="F38">
-        <v>-0.4832854290213925</v>
+        <v>-4.944711557223386</v>
       </c>
       <c r="G38">
-        <v>-7.886378818105136</v>
+        <v>-17.17141552594382</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.718787369947606</v>
       </c>
       <c r="E39">
-        <v>-24.47034046146961</v>
+        <v>-35.94455393854971</v>
       </c>
       <c r="F39">
-        <v>-0.3940512072896214</v>
+        <v>-4.837013026083214</v>
       </c>
       <c r="G39">
-        <v>-8.146202347289766</v>
+        <v>-16.49201727412066</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.462000270234846</v>
       </c>
       <c r="E40">
-        <v>-24.47794376932849</v>
+        <v>-35.54739318265499</v>
       </c>
       <c r="F40">
-        <v>-0.5963550944013166</v>
+        <v>-4.458659528324151</v>
       </c>
       <c r="G40">
-        <v>-7.567801735677089</v>
+        <v>-16.41062001089551</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.166262525147172</v>
       </c>
       <c r="E41">
-        <v>-22.91533494281974</v>
+        <v>-35.68081561234298</v>
       </c>
       <c r="F41">
-        <v>-0.4296486396901245</v>
+        <v>-4.868563055353639</v>
       </c>
       <c r="G41">
-        <v>-7.397919770658398</v>
+        <v>-16.55985324864061</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.842067868993174</v>
       </c>
       <c r="E42">
-        <v>-22.78072605294173</v>
+        <v>-34.93283623931105</v>
       </c>
       <c r="F42">
-        <v>-0.3314042657181032</v>
+        <v>-4.109126589243289</v>
       </c>
       <c r="G42">
-        <v>-7.110711166338644</v>
+        <v>-16.12793457049545</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.50757806873551</v>
       </c>
       <c r="E43">
-        <v>-22.42373738996907</v>
+        <v>-34.82873567882272</v>
       </c>
       <c r="F43">
-        <v>-0.5588375063611243</v>
+        <v>-4.593866484176489</v>
       </c>
       <c r="G43">
-        <v>-6.910212122948774</v>
+        <v>-15.93410789114671</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.175740280165162</v>
       </c>
       <c r="E44">
-        <v>-21.86502332385071</v>
+        <v>-34.70703520410359</v>
       </c>
       <c r="F44">
-        <v>-0.6172175274408221</v>
+        <v>-5.012433077504455</v>
       </c>
       <c r="G44">
-        <v>-6.846917359067086</v>
+        <v>-15.70764618216774</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.86589095630289</v>
       </c>
       <c r="E45">
-        <v>-21.14239661255072</v>
+        <v>-34.41611471266583</v>
       </c>
       <c r="F45">
-        <v>-0.7628163523612801</v>
+        <v>-4.515037385391283</v>
       </c>
       <c r="G45">
-        <v>-7.532978131266702</v>
+        <v>-17.32858931986278</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.587736934472598</v>
       </c>
       <c r="E46">
-        <v>-20.36446364819505</v>
+        <v>-34.67897904338907</v>
       </c>
       <c r="F46">
-        <v>-0.5127090391688309</v>
+        <v>-4.479788695667358</v>
       </c>
       <c r="G46">
-        <v>-7.280862191525209</v>
+        <v>-16.11498030777876</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.354967828062518</v>
       </c>
       <c r="E47">
-        <v>-20.57362027718732</v>
+        <v>-32.90000652150484</v>
       </c>
       <c r="F47">
-        <v>-0.7159986834898576</v>
+        <v>-3.382819849040502</v>
       </c>
       <c r="G47">
-        <v>-6.962249015660007</v>
+        <v>-15.77211234214615</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.167927681113262</v>
       </c>
       <c r="E48">
-        <v>-20.18785769036992</v>
+        <v>-34.06315186308598</v>
       </c>
       <c r="F48">
-        <v>-0.692657775181176</v>
+        <v>-4.861721568973918</v>
       </c>
       <c r="G48">
-        <v>-7.153921573054971</v>
+        <v>-15.79918077940079</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.029794136955698</v>
       </c>
       <c r="E49">
-        <v>-18.89169521752447</v>
+        <v>-34.04295034053776</v>
       </c>
       <c r="F49">
-        <v>-0.8711784057910946</v>
+        <v>-4.572708323974185</v>
       </c>
       <c r="G49">
-        <v>-7.679212332506475</v>
+        <v>-16.22882064917292</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.933089278137673</v>
       </c>
       <c r="E50">
-        <v>-18.71239481766477</v>
+        <v>-32.76943023773066</v>
       </c>
       <c r="F50">
-        <v>-0.7980269371846759</v>
+        <v>-4.688101559918961</v>
       </c>
       <c r="G50">
-        <v>-7.17153517038607</v>
+        <v>-17.49300148854188</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.873726784637372</v>
       </c>
       <c r="E51">
-        <v>-18.28283735871918</v>
+        <v>-31.22899734843747</v>
       </c>
       <c r="F51">
-        <v>-0.9983642800821251</v>
+        <v>-4.434982302849933</v>
       </c>
       <c r="G51">
-        <v>-7.492172859953448</v>
+        <v>-15.79740071670479</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.841295539969157</v>
       </c>
       <c r="E52">
-        <v>-17.89687099057143</v>
+        <v>-29.40085692001495</v>
       </c>
       <c r="F52">
-        <v>-0.9785977771165233</v>
+        <v>-5.054306221348567</v>
       </c>
       <c r="G52">
-        <v>-7.071566193134468</v>
+        <v>-15.10673639065727</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.829224464299979</v>
       </c>
       <c r="E53">
-        <v>-17.22495413120933</v>
+        <v>-31.41731846852045</v>
       </c>
       <c r="F53">
-        <v>-0.9226937462037931</v>
+        <v>-4.529855221492561</v>
       </c>
       <c r="G53">
-        <v>-7.146318982701738</v>
+        <v>-17.62906226233659</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.82820343264902</v>
       </c>
       <c r="E54">
-        <v>-16.68477510920437</v>
+        <v>-30.27972730576459</v>
       </c>
       <c r="F54">
-        <v>-0.8354210984818512</v>
+        <v>-4.134825031180338</v>
       </c>
       <c r="G54">
-        <v>-7.922291788073259</v>
+        <v>-17.00740038507342</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.831587602925482</v>
       </c>
       <c r="E55">
-        <v>-16.41442068247245</v>
+        <v>-29.44089995142778</v>
       </c>
       <c r="F55">
-        <v>-1.055200224323005</v>
+        <v>-4.284366884938121</v>
       </c>
       <c r="G55">
-        <v>-7.928562202473358</v>
+        <v>-16.37193768993122</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.83345071098265</v>
       </c>
       <c r="E56">
-        <v>-15.54520273907016</v>
+        <v>-29.74893807461454</v>
       </c>
       <c r="F56">
-        <v>-0.8439068941561293</v>
+        <v>-4.31089369427797</v>
       </c>
       <c r="G56">
-        <v>-7.905347559940286</v>
+        <v>-16.96920860673226</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.830367257224361</v>
       </c>
       <c r="E57">
-        <v>-15.7997437345673</v>
+        <v>-28.2597267548221</v>
       </c>
       <c r="F57">
-        <v>-0.8624772345920886</v>
+        <v>-4.144402615091506</v>
       </c>
       <c r="G57">
-        <v>-8.118558055651445</v>
+        <v>-16.66478179227932</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.823553425952273</v>
       </c>
       <c r="E58">
-        <v>-15.23455395061798</v>
+        <v>-30.67651219831667</v>
       </c>
       <c r="F58">
-        <v>-1.236399795113577</v>
+        <v>-4.927641390153897</v>
       </c>
       <c r="G58">
-        <v>-8.355160379859884</v>
+        <v>-16.11017167758339</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.814765421050679</v>
       </c>
       <c r="E59">
-        <v>-14.56959735580567</v>
+        <v>-29.06129835349781</v>
       </c>
       <c r="F59">
-        <v>-0.7991808529767755</v>
+        <v>-5.064747792460855</v>
       </c>
       <c r="G59">
-        <v>-8.196428005700186</v>
+        <v>-17.11218947679584</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.811748811312097</v>
       </c>
       <c r="E60">
-        <v>-14.41642172249622</v>
+        <v>-29.5865583178845</v>
       </c>
       <c r="F60">
-        <v>-0.8110190515301833</v>
+        <v>-4.879897606526145</v>
       </c>
       <c r="G60">
-        <v>-8.903970935449488</v>
+        <v>-18.60862502180698</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.819850062927858</v>
       </c>
       <c r="E61">
-        <v>-14.59318164843762</v>
+        <v>-26.39482870287932</v>
       </c>
       <c r="F61">
-        <v>-1.118614234109515</v>
+        <v>-4.549493327510729</v>
       </c>
       <c r="G61">
-        <v>-8.391375222211476</v>
+        <v>-18.0697483644886</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.850295327742929</v>
       </c>
       <c r="E62">
-        <v>-14.20833834184377</v>
+        <v>-27.54800913740659</v>
       </c>
       <c r="F62">
-        <v>-1.27119536786817</v>
+        <v>-4.362800852472192</v>
       </c>
       <c r="G62">
-        <v>-8.371970077908919</v>
+        <v>-17.52166624008519</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.908447485444562</v>
       </c>
       <c r="E63">
-        <v>-13.98636160293579</v>
+        <v>-29.0246312994577</v>
       </c>
       <c r="F63">
-        <v>-1.277711305858591</v>
+        <v>-4.621889325045794</v>
       </c>
       <c r="G63">
-        <v>-8.794620945759434</v>
+        <v>-17.85791106000006</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.00311765139687</v>
       </c>
       <c r="E64">
-        <v>-13.46535161140529</v>
+        <v>-28.34104909105184</v>
       </c>
       <c r="F64">
-        <v>-0.9656619917544063</v>
+        <v>-4.818127906034191</v>
       </c>
       <c r="G64">
-        <v>-9.345449452608097</v>
+        <v>-18.0576849534253</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.135078431809906</v>
       </c>
       <c r="E65">
-        <v>-13.25126800269268</v>
+        <v>-26.53226788901212</v>
       </c>
       <c r="F65">
-        <v>-1.079217908799774</v>
+        <v>-5.066895749136314</v>
       </c>
       <c r="G65">
-        <v>-9.454707568094486</v>
+        <v>-18.22328000247657</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.307567452888207</v>
       </c>
       <c r="E66">
-        <v>-13.68730117946923</v>
+        <v>-27.67917638703876</v>
       </c>
       <c r="F66">
-        <v>-1.641507903248258</v>
+        <v>-4.801374175312572</v>
       </c>
       <c r="G66">
-        <v>-9.420143180187296</v>
+        <v>-17.64672835921264</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.516550569793194</v>
       </c>
       <c r="E67">
-        <v>-13.14860749693879</v>
+        <v>-27.26649655071976</v>
       </c>
       <c r="F67">
-        <v>-1.350814729155648</v>
+        <v>-4.719514908567924</v>
       </c>
       <c r="G67">
-        <v>-9.209229539567749</v>
+        <v>-17.17522830539589</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.760840209922862</v>
       </c>
       <c r="E68">
-        <v>-13.237877305052</v>
+        <v>-29.55765533253054</v>
       </c>
       <c r="F68">
-        <v>-1.557614994529739</v>
+        <v>-4.624147454585826</v>
       </c>
       <c r="G68">
-        <v>-8.790289733300966</v>
+        <v>-17.55284932917537</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.033316032927379</v>
       </c>
       <c r="E69">
-        <v>-12.36886767145406</v>
+        <v>-27.8033562012771</v>
       </c>
       <c r="F69">
-        <v>-1.412184328192049</v>
+        <v>-5.145000026444071</v>
       </c>
       <c r="G69">
-        <v>-9.565002549593661</v>
+        <v>-17.34641947781681</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.329532105240899</v>
       </c>
       <c r="E70">
-        <v>-12.90270682984828</v>
+        <v>-26.42915906433147</v>
       </c>
       <c r="F70">
-        <v>-1.662406784453487</v>
+        <v>-5.443137738385641</v>
       </c>
       <c r="G70">
-        <v>-9.270480102417904</v>
+        <v>-18.49915854875157</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.640655883047421</v>
       </c>
       <c r="E71">
-        <v>-12.81479556393738</v>
+        <v>-30.22847177270877</v>
       </c>
       <c r="F71">
-        <v>-1.519266553984538</v>
+        <v>-5.728024056984627</v>
       </c>
       <c r="G71">
-        <v>-9.19185219018893</v>
+        <v>-17.86203391488951</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.960256465736632</v>
       </c>
       <c r="E72">
-        <v>-13.33874453509885</v>
+        <v>-28.9410900109642</v>
       </c>
       <c r="F72">
-        <v>-1.723678636136358</v>
+        <v>-5.500456620822352</v>
       </c>
       <c r="G72">
-        <v>-9.239666150753159</v>
+        <v>-16.63325253431461</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.279235372980412</v>
       </c>
       <c r="E73">
-        <v>-13.63108470313801</v>
+        <v>-28.79771852388135</v>
       </c>
       <c r="F73">
-        <v>-1.606743808454972</v>
+        <v>-4.757177460903606</v>
       </c>
       <c r="G73">
-        <v>-8.514440718020008</v>
+        <v>-17.79972679869721</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.59075171325016</v>
       </c>
       <c r="E74">
-        <v>-14.15772811633405</v>
+        <v>-25.66551343547</v>
       </c>
       <c r="F74">
-        <v>-1.567755039907407</v>
+        <v>-5.579820844949768</v>
       </c>
       <c r="G74">
-        <v>-9.051406063780018</v>
+        <v>-18.5912525942605</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.886852515827929</v>
       </c>
       <c r="E75">
-        <v>-14.04467023425855</v>
+        <v>-28.65281188410991</v>
       </c>
       <c r="F75">
-        <v>-1.865370052017811</v>
+        <v>-5.261347541636873</v>
       </c>
       <c r="G75">
-        <v>-9.170009098267707</v>
+        <v>-15.59075266411252</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.161556744453389</v>
       </c>
       <c r="E76">
-        <v>-14.55510623898113</v>
+        <v>-29.63458052049884</v>
       </c>
       <c r="F76">
-        <v>-1.955730025049986</v>
+        <v>-5.598706793366193</v>
       </c>
       <c r="G76">
-        <v>-9.1263196332037</v>
+        <v>-17.37893802408168</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.40906774360224</v>
       </c>
       <c r="E77">
-        <v>-14.6397479466585</v>
+        <v>-30.85463745917138</v>
       </c>
       <c r="F77">
-        <v>-1.886622646104035</v>
+        <v>-6.782894858017511</v>
       </c>
       <c r="G77">
-        <v>-8.392093809732994</v>
+        <v>-17.03088572838514</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.626229302886492</v>
       </c>
       <c r="E78">
-        <v>-15.37830130104346</v>
+        <v>-28.06338117879753</v>
       </c>
       <c r="F78">
-        <v>-2.14671841343944</v>
+        <v>-5.180032512275865</v>
       </c>
       <c r="G78">
-        <v>-7.94343597980232</v>
+        <v>-17.50664808900761</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.810738736958393</v>
       </c>
       <c r="E79">
-        <v>-15.08114736513414</v>
+        <v>-29.51129055140301</v>
       </c>
       <c r="F79">
-        <v>-1.971911353896272</v>
+        <v>-6.03681208862399</v>
       </c>
       <c r="G79">
-        <v>-8.697135853228332</v>
+        <v>-18.37450494170826</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.962562264548075</v>
       </c>
       <c r="E80">
-        <v>-16.32266927060304</v>
+        <v>-30.34041112170437</v>
       </c>
       <c r="F80">
-        <v>-2.054101967602039</v>
+        <v>-5.544649193394303</v>
       </c>
       <c r="G80">
-        <v>-8.36960759838612</v>
+        <v>-17.04648629628952</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.081296851657596</v>
       </c>
       <c r="E81">
-        <v>-16.05990909478197</v>
+        <v>-30.32447995014539</v>
       </c>
       <c r="F81">
-        <v>-2.03406707359793</v>
+        <v>-5.708334592187486</v>
       </c>
       <c r="G81">
-        <v>-8.131627161122713</v>
+        <v>-16.27888060589459</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.168652445702682</v>
       </c>
       <c r="E82">
-        <v>-17.4676441102284</v>
+        <v>-32.48699384234627</v>
       </c>
       <c r="F82">
-        <v>-2.121951884830541</v>
+        <v>-6.092165255213859</v>
       </c>
       <c r="G82">
-        <v>-7.855617365985342</v>
+        <v>-16.88518144442722</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.225901727387175</v>
       </c>
       <c r="E83">
-        <v>-18.9472097803845</v>
+        <v>-34.18804264774352</v>
       </c>
       <c r="F83">
-        <v>-2.403391366666479</v>
+        <v>-6.330037996050661</v>
       </c>
       <c r="G83">
-        <v>-7.60183456569165</v>
+        <v>-14.34949936039018</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.255927219832105</v>
       </c>
       <c r="E84">
-        <v>-19.62179843941112</v>
+        <v>-33.83904221292038</v>
       </c>
       <c r="F84">
-        <v>-2.27780092799324</v>
+        <v>-6.592213793934496</v>
       </c>
       <c r="G84">
-        <v>-7.349626751746491</v>
+        <v>-16.23725502919147</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.26110608159353</v>
       </c>
       <c r="E85">
-        <v>-20.70634079340413</v>
+        <v>-32.90047748280163</v>
       </c>
       <c r="F85">
-        <v>-2.623674139888534</v>
+        <v>-5.661316458404586</v>
       </c>
       <c r="G85">
-        <v>-7.373044830016249</v>
+        <v>-14.85203977015927</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.244572388232698</v>
       </c>
       <c r="E86">
-        <v>-20.72751140938999</v>
+        <v>-34.52724120057705</v>
       </c>
       <c r="F86">
-        <v>-2.464805697542631</v>
+        <v>-6.032533570988531</v>
       </c>
       <c r="G86">
-        <v>-6.861098798647006</v>
+        <v>-14.13914844926807</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.208566046803889</v>
       </c>
       <c r="E87">
-        <v>-22.06559396612444</v>
+        <v>-32.51486659986348</v>
       </c>
       <c r="F87">
-        <v>-2.401701497164768</v>
+        <v>-6.008571387127749</v>
       </c>
       <c r="G87">
-        <v>-6.739089856180613</v>
+        <v>-15.39335273448554</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.154666141109886</v>
       </c>
       <c r="E88">
-        <v>-23.08432400736397</v>
+        <v>-34.21330926846932</v>
       </c>
       <c r="F88">
-        <v>-2.736547482193995</v>
+        <v>-7.001542848170143</v>
       </c>
       <c r="G88">
-        <v>-6.662863798133153</v>
+        <v>-15.05803321905043</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.081944076534429</v>
       </c>
       <c r="E89">
-        <v>-23.94275059720598</v>
+        <v>-35.01110864829663</v>
       </c>
       <c r="F89">
-        <v>-2.807525314735468</v>
+        <v>-5.825894837257986</v>
       </c>
       <c r="G89">
-        <v>-6.900388145599797</v>
+        <v>-14.79591447538497</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.987895103791107</v>
       </c>
       <c r="E90">
-        <v>-26.25736687437649</v>
+        <v>-37.3579336968467</v>
       </c>
       <c r="F90">
-        <v>-2.750016736163515</v>
+        <v>-6.485661309096097</v>
       </c>
       <c r="G90">
-        <v>-6.299622727837945</v>
+        <v>-15.97975132364937</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.869830944918602</v>
       </c>
       <c r="E91">
-        <v>-27.38157866067669</v>
+        <v>-37.74421026546398</v>
       </c>
       <c r="F91">
-        <v>-3.004647763742652</v>
+        <v>-5.335555178681861</v>
       </c>
       <c r="G91">
-        <v>-6.189212903584189</v>
+        <v>-13.71697499915446</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.725450752115345</v>
       </c>
       <c r="E92">
-        <v>-29.15852016196848</v>
+        <v>-38.28651314177853</v>
       </c>
       <c r="F92">
-        <v>-2.773876202466349</v>
+        <v>-6.262938165505394</v>
       </c>
       <c r="G92">
-        <v>-6.403158392924663</v>
+        <v>-16.44357824084935</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.554760751159011</v>
       </c>
       <c r="E93">
-        <v>-30.87431594297171</v>
+        <v>-40.41373890027464</v>
       </c>
       <c r="F93">
-        <v>-3.097545026129603</v>
+        <v>-5.39352432952977</v>
       </c>
       <c r="G93">
-        <v>-6.39768203414195</v>
+        <v>-14.81701765184454</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.357629961689928</v>
       </c>
       <c r="E94">
-        <v>-33.29255502662274</v>
+        <v>-41.88100070655189</v>
       </c>
       <c r="F94">
-        <v>-3.415971112500538</v>
+        <v>-6.671546125916903</v>
       </c>
       <c r="G94">
-        <v>-6.1873754195109</v>
+        <v>-15.05896836719487</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.13784841040744</v>
       </c>
       <c r="E95">
-        <v>-35.26781651860644</v>
+        <v>-41.31974163804124</v>
       </c>
       <c r="F95">
-        <v>-3.385985040886599</v>
+        <v>-6.535162888352589</v>
       </c>
       <c r="G95">
-        <v>-7.114356603491187</v>
+        <v>-14.57673871887874</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.897646145406523</v>
       </c>
       <c r="E96">
-        <v>-36.72039248367683</v>
+        <v>-44.73375366394991</v>
       </c>
       <c r="F96">
-        <v>-3.403275553685233</v>
+        <v>-6.959246822766901</v>
       </c>
       <c r="G96">
-        <v>-6.911462268362922</v>
+        <v>-14.01264095204368</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.645836026274008</v>
       </c>
       <c r="E97">
-        <v>-38.77487283571372</v>
+        <v>-47.21187955211538</v>
       </c>
       <c r="F97">
-        <v>-3.647838603850745</v>
+        <v>-6.659288773457679</v>
       </c>
       <c r="G97">
-        <v>-7.281908901202671</v>
+        <v>-15.77788729209077</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.386366413403671</v>
       </c>
       <c r="E98">
-        <v>-40.81461526909265</v>
+        <v>-47.33395589017714</v>
       </c>
       <c r="F98">
-        <v>-3.591964394164516</v>
+        <v>-7.207436879605571</v>
       </c>
       <c r="G98">
-        <v>-6.913217721897225</v>
+        <v>-16.31187821050714</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.134246249429417</v>
       </c>
       <c r="E99">
-        <v>-43.0473680573895</v>
+        <v>-47.8721808756478</v>
       </c>
       <c r="F99">
-        <v>-3.543214972509765</v>
+        <v>-6.88299974517622</v>
       </c>
       <c r="G99">
-        <v>-7.330536604713642</v>
+        <v>-15.72658867423041</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.891162171490242</v>
       </c>
       <c r="E100">
-        <v>-45.64349918548384</v>
+        <v>-51.35645217578548</v>
       </c>
       <c r="F100">
-        <v>-3.59767350230461</v>
+        <v>-6.782104595515241</v>
       </c>
       <c r="G100">
-        <v>-7.903667574501851</v>
+        <v>-15.2639692465643</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.679906376079771</v>
       </c>
       <c r="E101">
-        <v>-46.83053902016646</v>
+        <v>-51.26874355908642</v>
       </c>
       <c r="F101">
-        <v>-3.723099924232094</v>
+        <v>-7.581628245349267</v>
       </c>
       <c r="G101">
-        <v>-7.705508042083865</v>
+        <v>-14.75479912863435</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.489443258970351</v>
       </c>
       <c r="E102">
-        <v>-49.83902959504375</v>
+        <v>-54.06626724748688</v>
       </c>
       <c r="F102">
-        <v>-3.720734935297102</v>
+        <v>-7.635827081963335</v>
       </c>
       <c r="G102">
-        <v>-8.064726334747194</v>
+        <v>-17.22057970917976</v>
       </c>
     </row>
   </sheetData>
